--- a/outputs/homophobie/homophobie_scenario_julie_run001_stats.xlsx
+++ b/outputs/homophobie/homophobie_scenario_julie_run001_stats.xlsx
@@ -649,7 +649,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>LLM_confidence</t>
+          <t>confidence</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
